--- a/reports/pdf_rolling5_20260721.xlsx
+++ b/reports/pdf_rolling5_20260721.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,7 +171,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-13 ~ 2026-07-21  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-13 ~ 2026-07-21  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,592억   ·   현금 170억(3.9%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 14종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,237억   ·   현금 170억(3.9%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 14종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1386,7 +1391,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,085억   ·   현금 22억(0.6%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,823억   ·   현금 22억(0.6%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1482,7 +1487,7 @@
         <v>83</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>462569790</v>
+        <v>455525580</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1503,7 +1508,7 @@
         <v>-49</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-886145400</v>
+        <v>-872650800</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1526,7 +1531,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1120181400</v>
+        <v>1103122800</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1547,7 +1552,7 @@
         <v>-21</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-356195700</v>
+        <v>-350771400</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1570,7 +1575,7 @@
         <v>6</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>955647000</v>
+        <v>941094000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1591,7 +1596,7 @@
         <v>-12</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-848203200</v>
+        <v>-835286400</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1605,965 +1610,1223 @@
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="19" t="n"/>
-      <c r="G32" s="19" t="n"/>
-      <c r="H32" s="19" t="n"/>
-      <c r="I32" s="19" t="n"/>
-      <c r="J32" s="19" t="n"/>
-      <c r="K32" s="19" t="n"/>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="19" t="n"/>
-      <c r="F34" s="19" t="n"/>
-      <c r="G34" s="19" t="n"/>
-      <c r="H34" s="19" t="n"/>
-      <c r="I34" s="19" t="n"/>
-      <c r="J34" s="19" t="n"/>
-      <c r="K34" s="19" t="n"/>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 341억   ·   현금 3억(100.0%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 10종목  /  매도 15종목</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,434억   ·   현금 90억(3.6%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지  (신규)</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>8573250000</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.57%</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>0→350</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-452</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-11321244000</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>8.29%→3.11%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>750→298</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>2807403000</v>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>2.22%→2.32%</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>120→242</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>-2357040000</v>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>7.42%→7.37%</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>170→150</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>4427730000</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>1.55%→3.48%</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>61→130</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>-3533145000</v>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>3.90%→2.32%</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>49→30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>3243828000</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>4.81%→6.28%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>102→130</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>-2239188000</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>3.68%→2.95%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>79→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,246억   ·   현금 52억(2.2%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 3억(100.0%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 10종목  /  매도 15종목</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>심텍홀딩스  (신규)</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>395</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>124059625</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.37%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>0→395</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>에이프로</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-174</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-42225450</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>0.44%→0.31%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>601→427</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>113</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>203626000</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>2.48%→3.08%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>460→573</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>금양그린파워</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>-61138800</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>0.97%→0.79%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>574→466</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>110</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>76015500</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>6.67%→6.88%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>3,229→3,339</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-73</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-91461700</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>1.58%→1.30%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>422→349</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>96</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>320688000</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>6.33%→7.27%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>634→730</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>액트로</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-29</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-19448850</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>0.37%→0.31%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>183→154</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>191568750</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>5.32%→5.88%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>697→772</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-50468750</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>0.57%→0.42%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>95→70</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>125647000</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>2.37%→2.74%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>240→278</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>오로스테크놀로지</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-33753500</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>0.39%→0.29%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>85→63</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>94248000</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>2.05%→2.33%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>131→149</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>엘티씨</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-84150000</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>1.50%→1.24%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>107→89</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍홀딩스  (신규)</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>6</v>
+        <v>395</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>35904000</v>
+        <v>110402500</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.09%</t>
+          <t>0.00%→0.35%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>55→61</t>
+          <t>0→395</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>에이프로</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-13</v>
+        <v>-174</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-158457000</v>
+        <v>-40926540</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>3.64%→3.16%</t>
+          <t>0.45%→0.32%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>100→87</t>
+          <t>601→427</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>54774000</v>
+        <v>192416400</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.15%</t>
+          <t>2.49%→3.09%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>460→573</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>금양그린파워</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-12</v>
+        <v>-108</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-143514000</v>
+        <v>-60186240</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>3.47%→3.03%</t>
+          <t>1.02%→0.82%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>97→85</t>
+          <t>574→466</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>71139200</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>6.64%→6.84%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>3,229→3,339</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-73</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-85129680</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>1.56%→1.29%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>422→349</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>302169600</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>6.34%→7.27%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>634→730</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>액트로</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-17881980</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.30%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>183→154</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>185115000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>5.47%→6.03%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>697→772</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-49235000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.59%→0.44%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>95→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>118628400</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>2.38%→2.75%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>240→278</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-31274760</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>0.38%→0.28%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>85→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>86223600</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>1.99%→2.26%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>131→149</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-79876800</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>1.51%→1.25%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>107→89</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>36945600</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>1.08%→1.19%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>55→61</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-143327600</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>3.50%→3.04%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>100→87</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>51342000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>1.98%→2.14%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>73→79</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-118783200</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>3.05%→2.66%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>97→85</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
           <t>코스메카코리아</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n">
+      <c r="B55" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>36040000</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="C55" s="11" t="n">
+        <v>33325000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>0.11%→0.21%</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>5→10</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-132199200</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>3.55%→3.12%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>76→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>브이엠</t>
         </is>
       </c>
-      <c r="H48" s="15" t="n">
+      <c r="H56" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-82849500</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>4.13%→3.87%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
+      <c r="I56" s="15" t="n">
+        <v>-71982000</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>3.81%→3.57%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
         <is>
           <t>150→141</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="17" t="n"/>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="17" t="n"/>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
+    <row r="57">
+      <c r="A57" s="17" t="n"/>
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>올릭스  (편출)</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>-148639500</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>3.75%→3.30%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>76→67</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="17" t="n"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>올릭스  (편출)</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-104499000</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>0.31%→0.00%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
+      <c r="I57" s="15" t="n">
+        <v>-88855200</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>0.28%→0.00%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
         <is>
           <t>9→0</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="17" t="n"/>
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="17" t="n"/>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="17" t="n"/>
-      <c r="G51" s="14" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="17" t="n"/>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>ISC</t>
         </is>
       </c>
-      <c r="H51" s="15" t="n">
+      <c r="H58" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I51" s="15" t="n">
-        <v>-86275000</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>1.77%→1.51%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
+      <c r="I58" s="15" t="n">
+        <v>-81631200</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>1.78%→1.51%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
         <is>
           <t>48→41</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="17" t="n"/>
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="17" t="n"/>
-      <c r="D52" s="17" t="n"/>
-      <c r="E52" s="17" t="n"/>
-      <c r="G52" s="14" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
         <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H59" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>-69190000</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>1.49%→1.28%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
+      <c r="I59" s="15" t="n">
+        <v>-61490000</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>1.41%→1.21%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
         <is>
           <t>36→31</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="G53" s="14" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="17" t="n"/>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H60" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I53" s="15" t="n">
-        <v>-54825000</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>2.57%→2.40%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="I60" s="15" t="n">
+        <v>-53664000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>2.67%→2.49%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
         <is>
           <t>47→44</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 528억   ·   현금 9억(1.7%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 3종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 479억   ·   현금 1억(0.1%)      오늘 2026-07-21  vs  5일전 2026-07-13      매수 3종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="G56" s="7" t="inlineStr">
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="8" t="n"/>
-      <c r="J56" s="8" t="n"/>
-      <c r="K56" s="8" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="G64" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="H64" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr">
+      <c r="I64" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr">
+      <c r="J64" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="K64" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>큐리오시스</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n">
+      <c r="B65" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>480704000</v>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>1.59%→1.84%</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="C65" s="11" t="n">
+        <v>399671040</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>1.59%→1.62%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>297→593</t>
         </is>
       </c>
-      <c r="G58" s="14" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
         <is>
           <t>코오롱티슈진</t>
         </is>
       </c>
-      <c r="H58" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I58" s="15" t="n">
-        <v>-244922400</v>
-      </c>
-      <c r="J58" s="16" t="inlineStr">
-        <is>
-          <t>3.70%→2.24%</t>
-        </is>
-      </c>
-      <c r="K58" s="13" t="inlineStr">
-        <is>
-          <t>197→163</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="H65" s="15" t="n">
+        <v>-93</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-660225600</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>3.70%→1.49%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>197→104</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="B59" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="C59" s="11" t="n">
-        <v>570998400</v>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>6.84%→8.37%</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>187→215</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="B66" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>760820800</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>6.84%→9.09%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>187→225</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>에이비엘바이오</t>
         </is>
       </c>
-      <c r="H59" s="15" t="n">
+      <c r="H66" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I59" s="15" t="n">
-        <v>-280627200</v>
-      </c>
-      <c r="J59" s="16" t="inlineStr">
-        <is>
-          <t>7.06%→6.38%</t>
-        </is>
-      </c>
-      <c r="K59" s="13" t="inlineStr">
+      <c r="I66" s="15" t="n">
+        <v>-260582400</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>7.06%→6.26%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
         <is>
           <t>413→381</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="C60" s="11" t="n">
-        <v>702612000</v>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>3.07%→4.77%</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>46→64</t>
-        </is>
-      </c>
-      <c r="G60" s="14" t="inlineStr">
+      <c r="B67" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>1365552000</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>3.07%→6.28%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>46→82</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="H60" s="15" t="n">
+      <c r="H67" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I60" s="15" t="n">
-        <v>-264642400</v>
-      </c>
-      <c r="J60" s="16" t="inlineStr">
-        <is>
-          <t>9.02%→7.74%</t>
-        </is>
-      </c>
-      <c r="K60" s="13" t="inlineStr">
+      <c r="I67" s="15" t="n">
+        <v>-247799200</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>9.02%→7.66%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>359→337</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="18" t="inlineStr">
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B62" s="19" t="n"/>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="19" t="n"/>
-      <c r="F62" s="19" t="n"/>
-      <c r="G62" s="19" t="n"/>
-      <c r="H62" s="19" t="n"/>
-      <c r="I62" s="19" t="n"/>
-      <c r="J62" s="19" t="n"/>
-      <c r="K62" s="19" t="n"/>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="20" t="n"/>
+      <c r="F69" s="20" t="n"/>
+      <c r="G69" s="20" t="n"/>
+      <c r="H69" s="20" t="n"/>
+      <c r="I69" s="20" t="n"/>
+      <c r="J69" s="20" t="n"/>
+      <c r="K69" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="G26:K26"/>
-    <mergeCell ref="G56:K56"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A4:E4"/>
+  <mergeCells count="20">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A41:K41"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G63:K63"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260721.xlsx
+++ b/reports/pdf_rolling5_20260721.xlsx
@@ -1810,23 +1810,23 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-3533145000</v>
+        <v>-2239188000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>3.90%→2.32%</t>
+          <t>3.68%→2.95%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>49→30</t>
+          <t>79→60</t>
         </is>
       </c>
     </row>
@@ -1854,23 +1854,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2239188000</v>
+        <v>-3533145000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>3.68%→2.95%</t>
+          <t>3.90%→2.32%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>79→60</t>
+          <t>49→30</t>
         </is>
       </c>
     </row>
@@ -2298,23 +2298,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>36945600</v>
+        <v>51342000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>1.08%→1.19%</t>
+          <t>1.98%→2.14%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>55→61</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2342,23 +2342,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>51342000</v>
+        <v>36945600</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.98%→2.14%</t>
+          <t>1.08%→1.19%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>55→61</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2407,23 +2407,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>올릭스  (편출)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-132199200</v>
+        <v>-88855200</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>3.55%→3.12%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>76→67</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>올릭스  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-88855200</v>
+        <v>-132199200</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>3.55%→3.12%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>76→67</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260721.xlsx
+++ b/reports/pdf_rolling5_20260721.xlsx
@@ -2298,23 +2298,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>51342000</v>
+        <v>36945600</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>1.98%→2.14%</t>
+          <t>1.08%→1.19%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>55→61</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2342,23 +2342,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>36945600</v>
+        <v>51342000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.08%→1.19%</t>
+          <t>1.98%→2.14%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>55→61</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2407,23 +2407,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>올릭스  (편출)</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-88855200</v>
+        <v>-71982000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>3.81%→3.57%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>150→141</t>
         </is>
       </c>
     </row>
@@ -2435,23 +2435,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-71982000</v>
+        <v>-132199200</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.81%→3.57%</t>
+          <t>3.55%→3.12%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>150→141</t>
+          <t>76→67</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>올릭스  (편출)</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-132199200</v>
+        <v>-88855200</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>3.55%→3.12%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>76→67</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260721.xlsx
+++ b/reports/pdf_rolling5_20260721.xlsx
@@ -2407,23 +2407,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>올릭스  (편출)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-71982000</v>
+        <v>-88855200</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>3.81%→3.57%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>150→141</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>올릭스  (편출)</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-88855200</v>
+        <v>-71982000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>3.81%→3.57%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>150→141</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260721.xlsx
+++ b/reports/pdf_rolling5_20260721.xlsx
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>알멕  (편출)</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-463512000</v>
+        <v>-392088000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>0.58%→0.47%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>15→0</t>
+          <t>90→75</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀</t>
+          <t>알멕  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-392088000</v>
+        <v>-463512000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.47%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>90→75</t>
+          <t>15→0</t>
         </is>
       </c>
     </row>
@@ -1810,23 +1810,23 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2239188000</v>
+        <v>-3533145000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>3.68%→2.95%</t>
+          <t>3.90%→2.32%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>79→60</t>
+          <t>49→30</t>
         </is>
       </c>
     </row>
@@ -1854,23 +1854,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-3533145000</v>
+        <v>-2239188000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>3.90%→2.32%</t>
+          <t>3.68%→2.95%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>49→30</t>
+          <t>79→60</t>
         </is>
       </c>
     </row>
@@ -1997,11 +1997,11 @@
         <v>395</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>110402500</v>
+        <v>125519150</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.35%</t>
+          <t>0.00%→0.37%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2018,11 +2018,11 @@
         <v>-174</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-40926540</v>
+        <v>-42722220</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.32%</t>
+          <t>0.44%→0.31%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2041,11 +2041,11 @@
         <v>113</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>192416400</v>
+        <v>206021600</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.49%→3.09%</t>
+          <t>2.48%→3.08%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2062,11 +2062,11 @@
         <v>-108</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-60186240</v>
+        <v>-61858080</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.82%</t>
+          <t>0.97%→0.79%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2085,11 +2085,11 @@
         <v>110</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>71139200</v>
+        <v>76909800</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>6.64%→6.84%</t>
+          <t>6.67%→6.88%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2106,11 +2106,11 @@
         <v>-73</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-85129680</v>
+        <v>-92537720</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.29%</t>
+          <t>1.58%→1.30%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2129,11 +2129,11 @@
         <v>96</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>302169600</v>
+        <v>324460800</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>6.34%→7.27%</t>
+          <t>6.33%→7.27%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2150,11 +2150,11 @@
         <v>-29</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-17881980</v>
+        <v>-19677660</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.30%</t>
+          <t>0.37%→0.31%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2173,11 +2173,11 @@
         <v>75</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>185115000</v>
+        <v>193822500</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>5.47%→6.03%</t>
+          <t>5.32%→5.88%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2194,11 +2194,11 @@
         <v>-25</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-49235000</v>
+        <v>-51062500</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.44%</t>
+          <t>0.57%→0.42%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2217,11 +2217,11 @@
         <v>38</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>118628400</v>
+        <v>127125200</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.75%</t>
+          <t>2.37%→2.74%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2238,11 +2238,11 @@
         <v>-22</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-31274760</v>
+        <v>-34150600</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.28%</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2261,11 +2261,11 @@
         <v>18</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>86223600</v>
+        <v>95356800</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.26%</t>
+          <t>2.05%→2.33%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2282,11 +2282,11 @@
         <v>-18</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-79876800</v>
+        <v>-85140000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.51%→1.25%</t>
+          <t>1.50%→1.24%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2298,23 +2298,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>36945600</v>
+        <v>55418400</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>1.08%→1.19%</t>
+          <t>1.99%→2.15%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>55→61</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2326,11 +2326,11 @@
         <v>-13</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-143327600</v>
+        <v>-160321200</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>3.50%→3.04%</t>
+          <t>3.64%→3.16%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2342,23 +2342,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>51342000</v>
+        <v>36326400</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.98%→2.14%</t>
+          <t>0.98%→1.09%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>55→61</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2370,11 +2370,11 @@
         <v>-12</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-118783200</v>
+        <v>-145202400</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.05%→2.66%</t>
+          <t>3.47%→3.03%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2393,7 +2393,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>33325000</v>
+        <v>36464000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2407,23 +2407,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>올릭스  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-88855200</v>
+        <v>-150388200</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>3.75%→3.30%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>76→67</t>
         </is>
       </c>
     </row>
@@ -2435,23 +2435,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-132199200</v>
+        <v>-83824200</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.55%→3.12%</t>
+          <t>4.13%→3.87%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>76→67</t>
+          <t>150→141</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>올릭스  (편출)</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-71982000</v>
+        <v>-105728400</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>3.81%→3.57%</t>
+          <t>0.31%→0.00%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>150→141</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
@@ -2498,11 +2498,11 @@
         <v>-7</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-81631200</v>
+        <v>-87290000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.78%→1.51%</t>
+          <t>1.77%→1.51%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2526,11 +2526,11 @@
         <v>-5</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-61490000</v>
+        <v>-70004000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.41%→1.21%</t>
+          <t>1.49%→1.28%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2554,11 +2554,11 @@
         <v>-3</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-53664000</v>
+        <v>-55470000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.49%</t>
+          <t>2.57%→2.40%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
